--- a/день 2/excel/reports extended.xlsx
+++ b/день 2/excel/reports extended.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\408\Downloads\DigitalSupport-Team-EzKolobok\день 2\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C613DC52-8A42-46DE-88CF-D7B9B38E14FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BDDCB919-0203-45D3-9F72-70731C00D998}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8250" yWindow="3750" windowWidth="16605" windowHeight="8580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
